--- a/data/trans_dic/P5B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia</t>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,03</t>
+          <t>0,65; 5,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,27</t>
+          <t>0,56; 5,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,12</t>
+          <t>0,9; 4,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,86</t>
+          <t>0,3; 3,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
     </row>
@@ -793,47 +794,47 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>3,17%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,4</t>
+          <t>2,43; 8,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,45</t>
+          <t>1,08; 6,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,25</t>
+          <t>2,23; 7,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,5</t>
+          <t>1,29; 5,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,15</t>
+          <t>0,33; 3,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,83</t>
+          <t>2,75; 7,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,04</t>
+          <t>1,75; 5,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,35</t>
+          <t>0,35; 2,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
     </row>
@@ -938,7 +939,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -978,7 +979,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,09</t>
+          <t>0,56; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,69</t>
+          <t>1,51; 6,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 48,08</t>
+          <t>0,5; 51,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,22</t>
+          <t>0,65; 3,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,91</t>
+          <t>0,23; 2,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,04</t>
+          <t>0,97; 4,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 28,7</t>
+          <t>0,22; 32,06</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1074,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1083,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1093,17 +1094,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1113,7 +1114,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1123,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,86</t>
+          <t>2,96; 9,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,08</t>
+          <t>1,07; 6,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,33</t>
+          <t>0,49; 4,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,21</t>
+          <t>0,67; 3,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,45</t>
+          <t>1,61; 6,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,45</t>
+          <t>0,41; 3,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,7</t>
+          <t>0,38; 3,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,07</t>
+          <t>2,47; 7,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,91</t>
+          <t>2,88; 6,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,9</t>
+          <t>1,05; 4,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,98</t>
+          <t>0,63; 2,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,47</t>
+          <t>1,96; 5,16</t>
         </is>
       </c>
     </row>
@@ -1213,49 +1214,49 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
@@ -1263,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,46</t>
+          <t>2,55; 5,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,13</t>
+          <t>1,13; 3,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,77</t>
+          <t>1,07; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 19,72</t>
+          <t>0,5; 16,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,41</t>
+          <t>1,91; 4,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,59</t>
+          <t>0,84; 2,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,09</t>
+          <t>0,58; 2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,11</t>
+          <t>0,69; 2,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,31</t>
+          <t>2,64; 4,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,54</t>
+          <t>1,14; 2,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,11</t>
+          <t>0,93; 2,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 9,57</t>
+          <t>0,89; 9,47</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4605</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>685; 5680</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5088</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>666; 6512</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4229</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2784</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2000; 9134</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>586; 6053</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3208</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5805</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4094</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6490</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4867</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12295</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8961</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3185</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3038; 10594</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1391; 8198</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4632</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3142; 11113</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1999; 9228</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>578; 5868</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5284</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7306; 18742</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4940; 15413</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1153; 7834</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4804</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4021</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28229</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5496</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>28229</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>599; 5500</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3505</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1744; 7909</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>953; 97720</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4351</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4801</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5918</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1434; 7515</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>507; 6200</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2415; 10602</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>843; 120449</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9157</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4545</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3053</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5723</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>8317</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14880</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6533</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>11370</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4892; 15176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1550; 9180</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>817; 6867</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1125; 6264</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2533; 10186</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>636; 5373</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>606; 5738</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4454; 13768</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9274; 21860</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>3126; 12164</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2031; 9426</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>6808; 17940</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>19275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9636</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31282</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9741</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35195</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17986</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15655</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>41023</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>12821; 26356</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5359; 15093</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5589; 15446</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3343; 110326</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10112; 22704</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4495; 14371</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3294; 11606</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5221; 17062</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>27284; 46386</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>11532; 26127</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10137; 22690</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>12694; 134992</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Habitat-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,4</t>
+          <t>0,65; 5,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,51</t>
+          <t>0,56; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,17 +747,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,09</t>
+          <t>0,89; 4,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,12</t>
+          <t>0,3; 2,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 8,48</t>
+          <t>2,15; 8,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,38</t>
+          <t>1,11; 6,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,9</t>
+          <t>2,33; 8,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,97</t>
+          <t>1,41; 6,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,35</t>
+          <t>0,33; 3,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,05</t>
+          <t>2,92; 7,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,45</t>
+          <t>1,76; 5,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,4</t>
+          <t>0,35; 2,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,1</t>
+          <t>0,56; 5,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,85</t>
+          <t>1,47; 6,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 51,32</t>
+          <t>0,48; 52,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,41</t>
+          <t>0,51; 3,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,8</t>
+          <t>0,27; 2,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,27</t>
+          <t>1,06; 4,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 32,06</t>
+          <t>0,23; 34,36</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,18</t>
+          <t>2,94; 9,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,32</t>
+          <t>1,1; 6,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,13</t>
+          <t>0,47; 4,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,75</t>
+          <t>0,67; 3,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,49</t>
+          <t>1,61; 6,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,5</t>
+          <t>0,42; 3,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,63</t>
+          <t>0,39; 3,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,64</t>
+          <t>2,32; 8,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,78</t>
+          <t>2,87; 6,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,07</t>
+          <t>0,97; 3,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,91</t>
+          <t>0,65; 2,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,16</t>
+          <t>1,92; 5,15</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,24</t>
+          <t>2,7; 5,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,17</t>
+          <t>1,09; 3,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,95</t>
+          <t>1,04; 2,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 16,58</t>
+          <t>0,49; 18,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,3</t>
+          <t>2,0; 4,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,67</t>
+          <t>0,86; 2,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,03</t>
+          <t>0,55; 2,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,24</t>
+          <t>0,74; 2,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,5</t>
+          <t>2,58; 4,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,58</t>
+          <t>1,19; 2,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,08</t>
+          <t>0,91; 2,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,47</t>
+          <t>0,89; 10,9</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>685; 5680</t>
+          <t>688; 5606</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5088</t>
+          <t>0; 4949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>666; 6512</t>
+          <t>666; 6113</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1675,17 +1675,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>0; 4215</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2784</t>
+          <t>0; 2731</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2000; 9134</t>
+          <t>1996; 9114</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>586; 6053</t>
+          <t>584; 5293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3208</t>
+          <t>0; 2602</t>
         </is>
       </c>
     </row>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3038; 10594</t>
+          <t>2683; 10086</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1391; 8198</t>
+          <t>1424; 8780</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4632</t>
+          <t>0; 4014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1873,42 +1873,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3142; 11113</t>
+          <t>3276; 11844</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1999; 9228</t>
+          <t>2174; 9633</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>578; 5868</t>
+          <t>578; 5980</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5284</t>
+          <t>0; 5776</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7306; 18742</t>
+          <t>7769; 19091</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4940; 15413</t>
+          <t>4983; 15438</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1153; 7834</t>
+          <t>1148; 6881</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4804</t>
+          <t>0; 5540</t>
         </is>
       </c>
     </row>
@@ -2061,37 +2061,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>599; 5500</t>
+          <t>608; 5465</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3036</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1744; 7909</t>
+          <t>1700; 7633</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>953; 97720</t>
+          <t>919; 99992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4351</t>
+          <t>0; 4844</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4801</t>
+          <t>0; 5261</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5918</t>
+          <t>0; 6083</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1434; 7515</t>
+          <t>1129; 6703</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>507; 6200</t>
+          <t>609; 6246</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2415; 10602</t>
+          <t>2642; 10261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>843; 120449</t>
+          <t>879; 129080</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4892; 15176</t>
+          <t>4868; 15904</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1550; 9180</t>
+          <t>1601; 9218</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>817; 6867</t>
+          <t>789; 6888</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1125; 6264</t>
+          <t>1118; 6532</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2533; 10186</t>
+          <t>2519; 9534</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>636; 5373</t>
+          <t>643; 5261</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>606; 5738</t>
+          <t>611; 5440</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4454; 13768</t>
+          <t>4185; 14704</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9274; 21860</t>
+          <t>9262; 21428</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3126; 12164</t>
+          <t>2895; 11603</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2031; 9426</t>
+          <t>2124; 9469</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6808; 17940</t>
+          <t>6672; 17902</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12821; 26356</t>
+          <t>13613; 28203</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5359; 15093</t>
+          <t>5181; 16126</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5589; 15446</t>
+          <t>5434; 15144</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3343; 110326</t>
+          <t>3260; 121356</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10112; 22704</t>
+          <t>10573; 23863</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4495; 14371</t>
+          <t>4595; 14072</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3294; 11606</t>
+          <t>3152; 11816</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5221; 17062</t>
+          <t>5599; 16017</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27284; 46386</t>
+          <t>26612; 44725</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11532; 26127</t>
+          <t>12034; 26919</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10137; 22690</t>
+          <t>9970; 22026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12694; 134992</t>
+          <t>12678; 155409</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,54 +649,54 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,33</t>
+          <t>0,51; 5,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,37 +727,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,99</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,65; 6,03</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 5,17</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,49</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,05</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,94</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,08</t>
+          <t>0,92; 4,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,73</t>
+          <t>0,3; 3,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
     </row>
@@ -789,44 +789,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4,63%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 8,07</t>
+          <t>2,34; 8,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,83</t>
+          <t>1,3; 6,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,33; 3,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,13; 8,4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,09; 6,49</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,31</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,33; 8,42</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,41; 6,23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,33; 3,41</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,27</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,19</t>
+          <t>2,87; 6,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,45</t>
+          <t>1,72; 5,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,11</t>
+          <t>0,38; 2,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,07</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,62</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 52,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,56; 5,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>1,46; 6,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,45; 10,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,04</t>
+          <t>0,53; 3,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,82</t>
+          <t>0,4; 2,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,13</t>
+          <t>1,15; 4,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 34,36</t>
+          <t>0,27; 5,07</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,54%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,13%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,75%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,62</t>
+          <t>1,6; 6,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,35</t>
+          <t>0,42; 3,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,15</t>
+          <t>0,38; 3,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,91</t>
+          <t>2,63; 7,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,07</t>
+          <t>3,22; 9,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,43</t>
+          <t>1,06; 6,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,44</t>
+          <t>0,5; 4,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,16</t>
+          <t>0,66; 3,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,65</t>
+          <t>2,86; 6,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,88</t>
+          <t>0,99; 4,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,92</t>
+          <t>0,63; 3,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,15</t>
+          <t>2,0; 5,26</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,6</t>
+          <t>1,86; 4,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,39</t>
+          <t>0,88; 2,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,9</t>
+          <t>0,55; 2,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 18,24</t>
+          <t>0,71; 2,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,51</t>
+          <t>2,59; 5,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,62</t>
+          <t>1,18; 3,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,07</t>
+          <t>1,02; 2,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,11</t>
+          <t>0,5; 2,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,33</t>
+          <t>2,53; 4,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,66</t>
+          <t>1,21; 2,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,01</t>
+          <t>0,91; 2,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,9</t>
+          <t>0,75; 2,07</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,54 +1577,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2106</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1276</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2499</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4605</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4605</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2040</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>484</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>688; 5606</t>
+          <t>607; 6237</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1655,37 +1655,37 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4949</t>
+          <t>0; 3124</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 2511</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>687; 6343</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>666; 6113</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4041</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4215</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2731</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1996; 9114</t>
+          <t>2046; 9201</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>584; 5293</t>
+          <t>588; 6034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2602</t>
+          <t>0; 2729</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,44 +1785,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6490</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4867</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5805</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4094</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1145</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6490</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4867</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>12295</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>945</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2683; 10086</t>
+          <t>3294; 11615</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1424; 8780</t>
+          <t>2011; 10047</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4014</t>
+          <t>578; 5523</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0; 5208</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2665; 10494</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1405; 8340</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3493</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3276; 11844</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2174; 9633</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>578; 5980</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0; 5776</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7769; 19091</t>
+          <t>7631; 18155</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4983; 15438</t>
+          <t>4861; 15138</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1148; 6881</t>
+          <t>1238; 7878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 5540</t>
+          <t>0; 4881</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>997</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4021</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28229</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1494</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1475</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28229</t>
+          <t>4130</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>608; 5465</t>
+          <t>0; 4330</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3036</t>
+          <t>0; 4976</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1700; 7633</t>
+          <t>0; 5759</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>919; 99992</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4844</t>
+          <t>608; 5489</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5261</t>
+          <t>0; 3486</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6083</t>
+          <t>1679; 7549</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>713; 16914</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1129; 6703</t>
+          <t>1173; 7091</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>609; 6246</t>
+          <t>879; 6445</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2642; 10261</t>
+          <t>2867; 10542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>879; 129080</t>
+          <t>863; 16505</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5723</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>9157</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4545</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2914</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3053</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5723</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>10947</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4868; 15904</t>
+          <t>2514; 10125</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1601; 9218</t>
+          <t>646; 5954</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>789; 6888</t>
+          <t>609; 5859</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1118; 6532</t>
+          <t>4423; 13426</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2519; 9534</t>
+          <t>5317; 16302</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>643; 5261</t>
+          <t>1537; 9189</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>611; 5440</t>
+          <t>824; 7263</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4185; 14704</t>
+          <t>1096; 6612</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9262; 21428</t>
+          <t>9215; 22279</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2895; 11603</t>
+          <t>2969; 12199</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2124; 9469</t>
+          <t>2050; 9995</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6672; 17902</t>
+          <t>6679; 17613</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>19275</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9636</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>9356</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>31282</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>15919</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>16506</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13613; 28203</t>
+          <t>9852; 23333</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5181; 16126</t>
+          <t>4738; 14816</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5434; 15144</t>
+          <t>3160; 12253</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3260; 121356</t>
+          <t>4997; 15865</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10573; 23863</t>
+          <t>13041; 27491</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4595; 14072</t>
+          <t>5602; 15733</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3152; 11816</t>
+          <t>5349; 14758</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5599; 16017</t>
+          <t>3141; 17899</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26612; 44725</t>
+          <t>26158; 44427</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12034; 26919</t>
+          <t>12306; 25324</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9970; 22026</t>
+          <t>9986; 22931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12678; 155409</t>
+          <t>9948; 27531</t>
         </is>
       </c>
     </row>
